--- a/docs/deliverables/02_外部設計/外部設計書.xlsx
+++ b/docs/deliverables/02_外部設計/外部設計書.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文書管理" sheetId="1" r:id="Re99026d448cd4cce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="画面構成" sheetId="2" r:id="Rc47340f8a9ba47a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="画面遷移" sheetId="3" r:id="R61eb10d227fd49ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="共通レイアウト" sheetId="4" r:id="Rb936f674abc546b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="勤務表入出力" sheetId="5" r:id="Rc79c8fe3c15044bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="外部向けAPI" sheetId="6" r:id="R129581373a9f400b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ファイル仕様" sheetId="7" r:id="R777a1e3910d34cfe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="外部連携" sheetId="8" r:id="R709171ca987d491d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文書管理" sheetId="1" r:id="R8f86cb4515364d4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="画面構成" sheetId="2" r:id="Rd75ec4eb99ca43da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="画面遷移" sheetId="3" r:id="R039981497db94115"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="共通レイアウト" sheetId="4" r:id="R409204053d9841d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="勤務表入出力" sheetId="5" r:id="R7768d856343d4892"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="外部向けAPI" sheetId="6" r:id="R0de536d6ccac4000"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ファイル仕様" sheetId="7" r:id="Rbf07568c8d314d4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="外部連携" sheetId="8" r:id="R61966c73352c4525"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1501,19 +1501,19 @@
         <x:v>•</x:v>
       </x:c>
       <x:c r="B5" s="24" t="str">
-        <x:v>ヘッダー左端にクエリロゴ、右端にログイン中のユーザーIDを表示する。</x:v>
+        <x:v>ヘッダー左端にクエリロゴ、右端にログイン中利用者の氏名と所属部署だけを表示する。</x:v>
       </x:c>
       <x:c r="C5" s="24" t="str">
-        <x:v>ヘッダー左端にクエリロゴ、右端にログイン中のユーザーIDを表示する。</x:v>
+        <x:v>ヘッダー左端にクエリロゴ、右端にログイン中利用者の氏名と所属部署だけを表示する。</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
-        <x:v>ヘッダー左端にクエリロゴ、右端にログイン中のユーザーIDを表示する。</x:v>
+        <x:v>ヘッダー左端にクエリロゴ、右端にログイン中利用者の氏名と所属部署だけを表示する。</x:v>
       </x:c>
       <x:c r="E5" s="24" t="str">
-        <x:v>ヘッダー左端にクエリロゴ、右端にログイン中のユーザーIDを表示する。</x:v>
+        <x:v>ヘッダー左端にクエリロゴ、右端にログイン中利用者の氏名と所属部署だけを表示する。</x:v>
       </x:c>
       <x:c r="F5" s="24" t="str">
-        <x:v>ヘッダー左端にクエリロゴ、右端にログイン中のユーザーIDを表示する。</x:v>
+        <x:v>ヘッダー左端にクエリロゴ、右端にログイン中利用者の氏名と所属部署だけを表示する。</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="24" customHeight="1">
